--- a/backend/checkpoints/merkl/0x3d1d0e523fcededa84488c9ffe367d44f2a9f0bb00c23cad0fe7fc24b31e620b.xlsx
+++ b/backend/checkpoints/merkl/0x3d1d0e523fcededa84488c9ffe367d44f2a9f0bb00c23cad0fe7fc24b31e620b.xlsx
@@ -398,7 +398,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B36"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="66.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,185 +438,1010 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Compute Chain</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Base (8453)</v>
+        <v>Sub Type</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Distribution Chain</v>
+        <v>Compute Chain</v>
       </c>
       <c r="B6" t="str">
-        <v>Polygon (137)</v>
+        <v>Base (8453)</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Pool ID</v>
+        <v>Distribution Chain</v>
       </c>
       <c r="B7" t="str">
-        <v>0x727b2741ac2b2df8bc9185e1de972661519fc07b156057eeed9b07c50e08829b</v>
+        <v>Polygon (137)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Currency 0</v>
+        <v>Pool ID</v>
       </c>
       <c r="B8" t="str">
-        <v>0x0000000000000000000000000000000000000000</v>
+        <v>0x727b2741ac2b2df8bc9185e1de972661519fc07b156057eeed9b07c50e08829b</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Currency 1</v>
+        <v>Currency 0</v>
       </c>
       <c r="B9" t="str">
-        <v>0x09bE1692ca16e06f536F0038fF11D1dA8524aDB1</v>
+        <v>0x0000000000000000000000000000000000000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Reward Token Symbol</v>
+        <v>Currency 1</v>
       </c>
       <c r="B10" t="str">
-        <v>aglaMerkl</v>
+        <v>0x09bE1692ca16e06f536F0038fF11D1dA8524aDB1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Reward Token Address</v>
+        <v>Reward Token Symbol</v>
       </c>
       <c r="B11" t="str">
-        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+        <v>aglaMerkl</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Reward Token Decimals</v>
-      </c>
-      <c r="B12">
-        <v>18</v>
+        <v>Reward Token Address</v>
+      </c>
+      <c r="B12" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Total Reward Amount (aglaMerkl)</v>
-      </c>
-      <c r="B13" t="str">
-        <v>628.70356</v>
+        <v>Reward Token Decimals</v>
+      </c>
+      <c r="B13">
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Total Reward Amount (raw)</v>
+        <v>Total Campaign Reward Amount (aglaMerkl)</v>
       </c>
       <c r="B14" t="str">
-        <v>628703560000000000000</v>
+        <v>628.70356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Start Timestamp (UTC)</v>
+        <v>Total Campaign Reward Amount (raw)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-04-22T00:00:00.000Z</v>
+        <v>628703560000000000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>End Timestamp (UTC)</v>
+        <v>Total Fetched LP Rewards (aglaMerkl)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-04-28T00:00:00.000Z</v>
+        <v>628.70356</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Start Timestamp (unix)</v>
-      </c>
-      <c r="B17">
-        <v>1776816000</v>
+        <v>Total Fetched LP Rewards (raw)</v>
+      </c>
+      <c r="B17" t="str">
+        <v>628703560000000000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>End Timestamp (unix)</v>
-      </c>
-      <c r="B18">
-        <v>1777334400</v>
+        <v>Total Claimed (aglaMerkl)</v>
+      </c>
+      <c r="B18" t="str">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Creator Address</v>
+        <v>Total Claimed (raw)</v>
       </c>
       <c r="B19" t="str">
-        <v>0x2358CF87e62618663E781CE52EE7a7F777aC4e65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Status</v>
+        <v>Total Unclaimed / Pending (aglaMerkl)</v>
       </c>
       <c r="B20" t="str">
-        <v>FAILED</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Pre-Compute Status</v>
+        <v>Total Unclaimed / Pending (raw)</v>
       </c>
       <c r="B21" t="str">
-        <v>SUCCESS</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Status Error</v>
+        <v>Start Timestamp (UTC)</v>
       </c>
       <c r="B22" t="str">
-        <v>MANUAL_UNLOCK</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Live Merkle Root (used for breakdown)</v>
+        <v>End Timestamp (UTC)</v>
       </c>
       <c r="B23" t="str">
-        <v>0x2ff26fb168f80fe249626caa90243588f601d8f7eda13a29300e7003e8d21288</v>
+        <v>2026-04-28T00:00:00.000Z</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Created At</v>
+        <v>Start Timestamp (unix)</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-04-21T17:12:31.896Z</v>
+        <v>1776816000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Breakdown Fetch</v>
+        <v>End Timestamp (unix)</v>
       </c>
       <c r="B25" t="str">
-        <v>skipped: MERKL_API_KEY env var not set — /v4/diffs/breakdowns requires authentication</v>
+        <v>1777334400</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Creator Address</v>
+      </c>
+      <c r="B26" t="str">
+        <v>0x2358CF87e62618663E781CE52EE7a7F777aC4e65</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Status</v>
+      </c>
+      <c r="B27" t="str">
+        <v>FAILED</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Pre-Compute Status</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SUCCESS</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Computed Until</v>
+      </c>
+      <c r="B29">
+        <v>1777334400</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Status Error</v>
+      </c>
+      <c r="B30" t="str">
+        <v>MANUAL_UNLOCK</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-04-21T17:12:31.896Z</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Reward Endpoint</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/v4/rewards/</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Count Endpoint</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/v4/rewards/count</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Expected Recipients</v>
+      </c>
+      <c r="B34">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Fetched Recipients</v>
+      </c>
+      <c r="B35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Hide Creator/Admin</v>
+      </c>
+      <c r="B36" t="str">
+        <v>false</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:I25"/>
+  <cols>
+    <col min="1" max="1" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="62.83203125" customWidth="1"/>
+    <col min="9" max="9" width="42.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>lpAddress</v>
+      </c>
+      <c r="B1" t="str">
+        <v>reward_formatted</v>
+      </c>
+      <c r="C1" t="str">
+        <v>claimed_formatted</v>
+      </c>
+      <c r="D1" t="str">
+        <v>unclaimed_formatted</v>
+      </c>
+      <c r="E1" t="str">
+        <v>reward_raw</v>
+      </c>
+      <c r="F1" t="str">
+        <v>claimed_raw</v>
+      </c>
+      <c r="G1" t="str">
+        <v>unclaimed_raw</v>
+      </c>
+      <c r="H1" t="str">
+        <v>reason</v>
+      </c>
+      <c r="I1" t="str">
+        <v>rewardTokenAddress</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>0xE6A50d73a5276a5A7Ecb467538C4E5907a1Ae20a</v>
+      </c>
+      <c r="B2" t="str">
+        <v>234.158159546065194578</v>
+      </c>
+      <c r="C2" t="str">
+        <v>0</v>
+      </c>
+      <c r="D2" t="str">
+        <v>0</v>
+      </c>
+      <c r="E2" t="str">
+        <v>234158159546065194578</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0</v>
+      </c>
+      <c r="G2" t="str">
+        <v>0</v>
+      </c>
+      <c r="H2" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2178204_2364390491447167841</v>
+      </c>
+      <c r="I2" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>0x4078aF18Db3725336742a4DBC3255aB3982032BD</v>
+      </c>
+      <c r="B3" t="str">
+        <v>66.322340220858306414</v>
+      </c>
+      <c r="C3" t="str">
+        <v>0</v>
+      </c>
+      <c r="D3" t="str">
+        <v>0</v>
+      </c>
+      <c r="E3" t="str">
+        <v>66322340220858306414</v>
+      </c>
+      <c r="F3" t="str">
+        <v>0</v>
+      </c>
+      <c r="G3" t="str">
+        <v>0</v>
+      </c>
+      <c r="H3" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2179672_2364390491447167841</v>
+      </c>
+      <c r="I3" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>0x4078aF18Db3725336742a4DBC3255aB3982032BD</v>
+      </c>
+      <c r="B4" t="str">
+        <v>65.240807784684686108</v>
+      </c>
+      <c r="C4" t="str">
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <v>0</v>
+      </c>
+      <c r="E4" t="str">
+        <v>65240807784684686108</v>
+      </c>
+      <c r="F4" t="str">
+        <v>0</v>
+      </c>
+      <c r="G4" t="str">
+        <v>0</v>
+      </c>
+      <c r="H4" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2175757_2364390491447167841</v>
+      </c>
+      <c r="I4" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>0x8432E1Bb87D1A04FFabe9A9e8dbd470152e8E90A</v>
+      </c>
+      <c r="B5" t="str">
+        <v>35.498619616102869614</v>
+      </c>
+      <c r="C5" t="str">
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>0</v>
+      </c>
+      <c r="E5" t="str">
+        <v>35498619616102869614</v>
+      </c>
+      <c r="F5" t="str">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2193180_2364390491447167841</v>
+      </c>
+      <c r="I5" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>0x93E7fB017883f56fBc43f5723eCcCf6bF90FE6cF</v>
+      </c>
+      <c r="B6" t="str">
+        <v>33.768560979729245195</v>
+      </c>
+      <c r="C6" t="str">
+        <v>0</v>
+      </c>
+      <c r="D6" t="str">
+        <v>0</v>
+      </c>
+      <c r="E6" t="str">
+        <v>33768560979729245195</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>0</v>
+      </c>
+      <c r="H6" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2190020_2364390491447167841</v>
+      </c>
+      <c r="I6" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>0x93E7fB017883f56fBc43f5723eCcCf6bF90FE6cF</v>
+      </c>
+      <c r="B7" t="str">
+        <v>31.611993774821774016</v>
+      </c>
+      <c r="C7" t="str">
+        <v>0</v>
+      </c>
+      <c r="D7" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7" t="str">
+        <v>31611993774821774016</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2183289_2364390491447167841</v>
+      </c>
+      <c r="I7" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>0x8432E1Bb87D1A04FFabe9A9e8dbd470152e8E90A</v>
+      </c>
+      <c r="B8" t="str">
+        <v>28.693426910910457131</v>
+      </c>
+      <c r="C8" t="str">
+        <v>0</v>
+      </c>
+      <c r="D8" t="str">
+        <v>0</v>
+      </c>
+      <c r="E8" t="str">
+        <v>28693426910910457131</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2179648_2364390491447167841</v>
+      </c>
+      <c r="I8" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>0xa4fF2Ff7c9dCc78b76Ac381E2d06938B88bd8804</v>
+      </c>
+      <c r="B9" t="str">
+        <v>28.542960874527224351</v>
+      </c>
+      <c r="C9" t="str">
+        <v>0</v>
+      </c>
+      <c r="D9" t="str">
+        <v>0</v>
+      </c>
+      <c r="E9" t="str">
+        <v>28542960874527224351</v>
+      </c>
+      <c r="F9" t="str">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_504866_2364390491447167841</v>
+      </c>
+      <c r="I9" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>0x4dedbaF8f1bE09A82DBe5741174eA076AF52a90D</v>
+      </c>
+      <c r="B10" t="str">
+        <v>22.114946737246411492</v>
+      </c>
+      <c r="C10" t="str">
+        <v>0</v>
+      </c>
+      <c r="D10" t="str">
+        <v>0</v>
+      </c>
+      <c r="E10" t="str">
+        <v>22114946737246411492</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <v>0</v>
+      </c>
+      <c r="H10" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_942311_2364390491447167841</v>
+      </c>
+      <c r="I10" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>0x8432E1Bb87D1A04FFabe9A9e8dbd470152e8E90A</v>
+      </c>
+      <c r="B11" t="str">
+        <v>18.927081006309826861</v>
+      </c>
+      <c r="C11" t="str">
+        <v>0</v>
+      </c>
+      <c r="D11" t="str">
+        <v>0</v>
+      </c>
+      <c r="E11" t="str">
+        <v>18927081006309826861</v>
+      </c>
+      <c r="F11" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <v>0</v>
+      </c>
+      <c r="H11" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2191328_2364390491447167841</v>
+      </c>
+      <c r="I11" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>0xe3B1ebcD19c28459aD75B44C13095cA93E53cbB0</v>
+      </c>
+      <c r="B12" t="str">
+        <v>16.716278486298979154</v>
+      </c>
+      <c r="C12" t="str">
+        <v>0</v>
+      </c>
+      <c r="D12" t="str">
+        <v>0</v>
+      </c>
+      <c r="E12" t="str">
+        <v>16716278486298979154</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <v>0</v>
+      </c>
+      <c r="H12" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_639470_2364390491447167841</v>
+      </c>
+      <c r="I12" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>0xBa44825f3215A71b34a702A70373afF8d4A52390</v>
+      </c>
+      <c r="B13" t="str">
+        <v>15.758805910530316142</v>
+      </c>
+      <c r="C13" t="str">
+        <v>0</v>
+      </c>
+      <c r="D13" t="str">
+        <v>0</v>
+      </c>
+      <c r="E13" t="str">
+        <v>15758805910530316142</v>
+      </c>
+      <c r="F13" t="str">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <v>0</v>
+      </c>
+      <c r="H13" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_510443_2364390491447167841</v>
+      </c>
+      <c r="I13" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>0x4078aF18Db3725336742a4DBC3255aB3982032BD</v>
+      </c>
+      <c r="B14" t="str">
+        <v>10.360371981700233627</v>
+      </c>
+      <c r="C14" t="str">
+        <v>0</v>
+      </c>
+      <c r="D14" t="str">
+        <v>0</v>
+      </c>
+      <c r="E14" t="str">
+        <v>10360371981700233627</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H14" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2175681_2364390491447167841</v>
+      </c>
+      <c r="I14" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>0xc38eDb1B53c7c034867BdE801e24826687F24466</v>
+      </c>
+      <c r="B15" t="str">
+        <v>5.915509231061464273</v>
+      </c>
+      <c r="C15" t="str">
+        <v>0</v>
+      </c>
+      <c r="D15" t="str">
+        <v>0</v>
+      </c>
+      <c r="E15" t="str">
+        <v>5915509231061464273</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2184873_2364390491447167841</v>
+      </c>
+      <c r="I15" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>0xdcE6F2ccaf54de860a5f80DB7503154957d216D5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>3.622701712969794046</v>
+      </c>
+      <c r="C16" t="str">
+        <v>0</v>
+      </c>
+      <c r="D16" t="str">
+        <v>0</v>
+      </c>
+      <c r="E16" t="str">
+        <v>3622701712969794046</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <v>0</v>
+      </c>
+      <c r="H16" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2103468_2364390491447167841</v>
+      </c>
+      <c r="I16" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>0x4078aF18Db3725336742a4DBC3255aB3982032BD</v>
+      </c>
+      <c r="B17" t="str">
+        <v>3.608787647455019567</v>
+      </c>
+      <c r="C17" t="str">
+        <v>0</v>
+      </c>
+      <c r="D17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E17" t="str">
+        <v>3608787647455019567</v>
+      </c>
+      <c r="F17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G17" t="str">
+        <v>0</v>
+      </c>
+      <c r="H17" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2201813_2364390491447167841</v>
+      </c>
+      <c r="I17" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>0xCD7a60306d8315B0b611De60B38Ae0B623062b2e</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2.105966914746935271</v>
+      </c>
+      <c r="C18" t="str">
+        <v>0</v>
+      </c>
+      <c r="D18" t="str">
+        <v>0</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2105966914746935271</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0</v>
+      </c>
+      <c r="G18" t="str">
+        <v>0</v>
+      </c>
+      <c r="H18" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_757614_2364390491447167841</v>
+      </c>
+      <c r="I18" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>0x8432E1Bb87D1A04FFabe9A9e8dbd470152e8E90A</v>
+      </c>
+      <c r="B19" t="str">
+        <v>1.8024872987904498</v>
+      </c>
+      <c r="C19" t="str">
+        <v>0</v>
+      </c>
+      <c r="D19" t="str">
+        <v>0</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1802487298790449800</v>
+      </c>
+      <c r="F19" t="str">
+        <v>0</v>
+      </c>
+      <c r="G19" t="str">
+        <v>0</v>
+      </c>
+      <c r="H19" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2201716_2364390491447167841</v>
+      </c>
+      <c r="I19" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>0x4078aF18Db3725336742a4DBC3255aB3982032BD</v>
+      </c>
+      <c r="B20" t="str">
+        <v>1.710706792275525164</v>
+      </c>
+      <c r="C20" t="str">
+        <v>0</v>
+      </c>
+      <c r="D20" t="str">
+        <v>0</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1710706792275525164</v>
+      </c>
+      <c r="F20" t="str">
+        <v>0</v>
+      </c>
+      <c r="G20" t="str">
+        <v>0</v>
+      </c>
+      <c r="H20" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2203224_2364390491447167841</v>
+      </c>
+      <c r="I20" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>0x93E7fB017883f56fBc43f5723eCcCf6bF90FE6cF</v>
+      </c>
+      <c r="B21" t="str">
+        <v>1.371572786907528195</v>
+      </c>
+      <c r="C21" t="str">
+        <v>0</v>
+      </c>
+      <c r="D21" t="str">
+        <v>0</v>
+      </c>
+      <c r="E21" t="str">
+        <v>1371572786907528195</v>
+      </c>
+      <c r="F21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G21" t="str">
+        <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2202903_2364390491447167841</v>
+      </c>
+      <c r="I21" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>0x8432E1Bb87D1A04FFabe9A9e8dbd470152e8E90A</v>
+      </c>
+      <c r="B22" t="str">
+        <v>0.839026921962576876</v>
+      </c>
+      <c r="C22" t="str">
+        <v>0</v>
+      </c>
+      <c r="D22" t="str">
+        <v>0</v>
+      </c>
+      <c r="E22" t="str">
+        <v>839026921962576876</v>
+      </c>
+      <c r="F22" t="str">
+        <v>0</v>
+      </c>
+      <c r="G22" t="str">
+        <v>0</v>
+      </c>
+      <c r="H22" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_2203344_2364390491447167841</v>
+      </c>
+      <c r="I22" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>0xc1612C97537c2CC62a11FC4516367AB6F62d4B23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>0.006223432022590896</v>
+      </c>
+      <c r="C23" t="str">
+        <v>0</v>
+      </c>
+      <c r="D23" t="str">
+        <v>0</v>
+      </c>
+      <c r="E23" t="str">
+        <v>6223432022590896</v>
+      </c>
+      <c r="F23" t="str">
+        <v>0</v>
+      </c>
+      <c r="G23" t="str">
+        <v>0</v>
+      </c>
+      <c r="H23" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_473240_2364390491447167841</v>
+      </c>
+      <c r="I23" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>0xc1612C97537c2CC62a11FC4516367AB6F62d4B23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>0.006223432022590896</v>
+      </c>
+      <c r="C24" t="str">
+        <v>0</v>
+      </c>
+      <c r="D24" t="str">
+        <v>0</v>
+      </c>
+      <c r="E24" t="str">
+        <v>6223432022590896</v>
+      </c>
+      <c r="F24" t="str">
+        <v>0</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0</v>
+      </c>
+      <c r="H24" t="str">
+        <v>MultiLogPerAdditionalParam_tokenId_467685_2364390491447167841</v>
+      </c>
+      <c r="I24" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>0xeaC6A75e19beB1283352d24c0311De865a867DAB</v>
+      </c>
+      <c r="B25" t="str">
+        <v>0.000000000000000333</v>
+      </c>
+      <c r="C25" t="str">
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <v>0</v>
+      </c>
+      <c r="E25" t="str">
+        <v>333</v>
+      </c>
+      <c r="F25" t="str">
+        <v>0</v>
+      </c>
+      <c r="G25" t="str">
+        <v>0</v>
+      </c>
+      <c r="H25" t="str">
+        <v>roundingError</v>
+      </c>
+      <c r="I25" t="str">
+        <v>0xd8ef817FFb926370dCaAb8F758DDb99b03591A5e</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I25"/>
   </ignoredErrors>
 </worksheet>
 </file>